--- a/docs/Files/EV_model/ODYM_Tutorial6_RemeltingYieldLL_V1.0.xlsx
+++ b/docs/Files/EV_model/ODYM_Tutorial6_RemeltingYieldLL_V1.0.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF69358-A5C3-48F7-A885-7B88B11DC077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD1485F-5291-45F7-B8B5-351AE0DE06E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2390" yWindow="2020" windowWidth="14400" windowHeight="7280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="103">
   <si>
     <t>Format_Version</t>
   </si>
@@ -201,9 +201,6 @@
     <t>none</t>
   </si>
   <si>
-    <t>Waste mgt. Industries</t>
-  </si>
-  <si>
     <t>BAU</t>
   </si>
   <si>
@@ -270,9 +267,6 @@
     <t>sp</t>
   </si>
   <si>
-    <t>created parameter file and added values from literature</t>
-  </si>
-  <si>
     <t>Dataset</t>
   </si>
   <si>
@@ -318,21 +312,9 @@
     <t>ODYM_Tutorial6_RemeltingYield</t>
   </si>
   <si>
-    <t>DOI: 10.1016/j.resconrec.2016.09.029</t>
-  </si>
-  <si>
-    <t>Pauliuk et al. MaTrace Global paper</t>
-  </si>
-  <si>
-    <t>10.1016/j.resconrec.2016.09.029</t>
-  </si>
-  <si>
     <t>38ed7154-01c2-4d21-8128-df10bbd150a5</t>
   </si>
   <si>
-    <t>From MaTrace Global paper, DOI: 10.1016/j.resconrec.2016.09.029</t>
-  </si>
-  <si>
     <t>Remelting yield</t>
   </si>
   <si>
@@ -352,6 +334,12 @@
   </si>
   <si>
     <t>LIB materials</t>
+  </si>
+  <si>
+    <t>Recycling_Remelting</t>
+  </si>
+  <si>
+    <t>Scrap to refurbishment + Remelting yield = .66+.34</t>
   </si>
 </sst>
 </file>
@@ -767,15 +755,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H28"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.81640625" customWidth="1"/>
-    <col min="3" max="3" width="19.1796875" customWidth="1"/>
-    <col min="4" max="4" width="31.453125" customWidth="1"/>
+    <col min="1" max="1" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" customWidth="1"/>
+    <col min="3" max="3" width="19.21875" customWidth="1"/>
+    <col min="4" max="4" width="31.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>39</v>
       </c>
@@ -786,7 +774,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -800,12 +788,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>16</v>
@@ -814,12 +802,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
@@ -828,7 +816,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>1</v>
       </c>
@@ -842,7 +830,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
@@ -856,7 +844,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
@@ -870,12 +858,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>16</v>
@@ -884,12 +872,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>16</v>
@@ -898,12 +886,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>16</v>
@@ -912,7 +900,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>27</v>
       </c>
@@ -926,7 +914,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>29</v>
       </c>
@@ -940,7 +928,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>31</v>
       </c>
@@ -954,7 +942,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>34</v>
       </c>
@@ -968,12 +956,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>36</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>16</v>
@@ -982,37 +970,37 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>2</v>
       </c>
@@ -1032,7 +1020,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>10</v>
       </c>
@@ -1049,18 +1037,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>16</v>
@@ -1069,18 +1057,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" t="s">
         <v>64</v>
-      </c>
-      <c r="B24" t="s">
-        <v>65</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>16</v>
@@ -1089,18 +1077,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" t="s">
         <v>62</v>
-      </c>
-      <c r="B25" t="s">
-        <v>63</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>16</v>
@@ -1109,7 +1097,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C26" s="8" t="s">
         <v>14</v>
       </c>
@@ -1123,7 +1111,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C27" s="8" t="s">
         <v>15</v>
       </c>
@@ -1134,7 +1122,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E28" s="1" t="s">
         <v>16</v>
       </c>
@@ -1147,28 +1135,28 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H33"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="36.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="17.6328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.36328125" customWidth="1"/>
-    <col min="9" max="9" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" customWidth="1"/>
+    <col min="9" max="9" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>11</v>
@@ -1186,18 +1174,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0.34</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1209,21 +1197,21 @@
         <v>55</v>
       </c>
       <c r="H2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" t="s">
-        <v>105</v>
-      </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0.34</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -1235,25 +1223,25 @@
         <v>55</v>
       </c>
       <c r="H3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B4" s="1"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B5" s="1"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" s="1"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B7" s="1"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B8" s="1"/>
     </row>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E33" s="1"/>
     </row>
   </sheetData>
@@ -1264,47 +1252,47 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:M3"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B3" s="13">
         <v>43344</v>
       </c>
@@ -1312,14 +1300,12 @@
         <v>54</v>
       </c>
       <c r="E3" s="15"/>
-      <c r="F3" s="12" t="s">
-        <v>98</v>
+      <c r="F3" s="12" t="str">
+        <f>Cover!B10</f>
+        <v>38ed7154-01c2-4d21-8128-df10bbd150a5</v>
       </c>
       <c r="G3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1330,71 +1316,57 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:P3"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="O2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G3" t="s">
-        <v>96</v>
-      </c>
-      <c r="I3">
-        <v>2017</v>
-      </c>
-      <c r="L3" t="s">
-        <v>97</v>
+    </row>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B3" t="str">
+        <f>Cover!B3</f>
+        <v>ODYM_Tutorial6_RemeltingYield</v>
       </c>
     </row>
   </sheetData>
